--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -27995,6 +27995,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>12.6000003814697</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>12.8000001907349</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="G1202" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28018,6 +28018,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28041,6 +28041,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>18750</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>13</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28064,6 +28064,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>24500</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>13</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>13.1999998092651</v>
+      </c>
+      <c r="G1205" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -27905,22 +27905,22 @@
     </row>
     <row r="1198">
       <c r="A1198" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1198" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="C1198" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="D1198" t="n">
         <v>12.8000001907349</v>
       </c>
-      <c r="D1198" t="n">
-        <v>12.75</v>
-      </c>
       <c r="E1198" t="n">
-        <v>12.75</v>
+        <v>12.8000001907349</v>
       </c>
       <c r="F1198" t="n">
-        <v>12.8000001907349</v>
+        <v>12.8500003814697</v>
       </c>
       <c r="G1198" t="s">
         <v>7</v>
@@ -27928,19 +27928,19 @@
     </row>
     <row r="1199">
       <c r="A1199" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1199" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C1199" t="n">
         <v>12.8000001907349</v>
       </c>
       <c r="D1199" t="n">
-        <v>12.8000001907349</v>
+        <v>12.75</v>
       </c>
       <c r="E1199" t="n">
-        <v>12.8000001907349</v>
+        <v>12.75</v>
       </c>
       <c r="F1199" t="n">
         <v>12.8000001907349</v>
@@ -27951,22 +27951,22 @@
     </row>
     <row r="1200">
       <c r="A1200" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1200" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="C1200" t="n">
-        <v>12.8500003814697</v>
+        <v>12.8000001907349</v>
       </c>
       <c r="D1200" t="n">
-        <v>12.5500001907349</v>
+        <v>12.8000001907349</v>
       </c>
       <c r="E1200" t="n">
-        <v>12.5500001907349</v>
+        <v>12.8000001907349</v>
       </c>
       <c r="F1200" t="n">
-        <v>12.8500003814697</v>
+        <v>12.8000001907349</v>
       </c>
       <c r="G1200" t="s">
         <v>7</v>
@@ -27974,22 +27974,22 @@
     </row>
     <row r="1201">
       <c r="A1201" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1201" t="n">
-        <v>1250</v>
+        <v>3500</v>
       </c>
       <c r="C1201" t="n">
-        <v>12.8999996185303</v>
+        <v>12.8500003814697</v>
       </c>
       <c r="D1201" t="n">
-        <v>12.5</v>
+        <v>12.5500001907349</v>
       </c>
       <c r="E1201" t="n">
         <v>12.5500001907349</v>
       </c>
       <c r="F1201" t="n">
-        <v>12.8999996185303</v>
+        <v>12.8500003814697</v>
       </c>
       <c r="G1201" t="s">
         <v>7</v>
@@ -27997,19 +27997,19 @@
     </row>
     <row r="1202">
       <c r="A1202" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1202" t="n">
-        <v>2250</v>
+        <v>1250</v>
       </c>
       <c r="C1202" t="n">
         <v>12.8999996185303</v>
       </c>
       <c r="D1202" t="n">
-        <v>12.6000003814697</v>
+        <v>12.5</v>
       </c>
       <c r="E1202" t="n">
-        <v>12.8000001907349</v>
+        <v>12.5500001907349</v>
       </c>
       <c r="F1202" t="n">
         <v>12.8999996185303</v>
@@ -28020,22 +28020,22 @@
     </row>
     <row r="1203">
       <c r="A1203" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1203" t="n">
-        <v>4500</v>
+        <v>2250</v>
       </c>
       <c r="C1203" t="n">
-        <v>13</v>
+        <v>12.8999996185303</v>
       </c>
       <c r="D1203" t="n">
-        <v>12.8500003814697</v>
+        <v>12.6000003814697</v>
       </c>
       <c r="E1203" t="n">
-        <v>12.8500003814697</v>
+        <v>12.8000001907349</v>
       </c>
       <c r="F1203" t="n">
-        <v>13</v>
+        <v>12.8999996185303</v>
       </c>
       <c r="G1203" t="s">
         <v>7</v>
@@ -28043,19 +28043,19 @@
     </row>
     <row r="1204">
       <c r="A1204" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1204" t="n">
-        <v>18750</v>
+        <v>4500</v>
       </c>
       <c r="C1204" t="n">
         <v>13</v>
       </c>
       <c r="D1204" t="n">
-        <v>13</v>
+        <v>12.8500003814697</v>
       </c>
       <c r="E1204" t="n">
-        <v>13</v>
+        <v>12.8500003814697</v>
       </c>
       <c r="F1204" t="n">
         <v>13</v>
@@ -28066,24 +28066,47 @@
     </row>
     <row r="1205">
       <c r="A1205" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1205" t="n">
-        <v>24500</v>
+        <v>18750</v>
       </c>
       <c r="C1205" t="n">
-        <v>13.1999998092651</v>
+        <v>13</v>
       </c>
       <c r="D1205" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="E1205" t="n">
         <v>13</v>
       </c>
       <c r="F1205" t="n">
-        <v>13.1999998092651</v>
+        <v>13</v>
       </c>
       <c r="G1205" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1206" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>13.0500001907349</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>13.3500003814697</v>
+      </c>
+      <c r="G1206" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -31765,7 +31765,7 @@
         <v>12250</v>
       </c>
       <c r="C1208" t="n">
-        <v>14.1999998092651</v>
+        <v>14.25</v>
       </c>
       <c r="D1208" t="n">
         <v>13.75</v>
@@ -31780,6 +31780,32 @@
         <v>14.25</v>
       </c>
       <c r="H1208" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>13.9499998092651</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="H1209" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -31809,6 +31809,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>14.1000003814697</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -31835,6 +31835,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1211">
+      <c r="A1211" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1211" t="n">
+        <v>31250</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="G1211" t="n">
+        <v>14.3000001907349</v>
+      </c>
+      <c r="H1211" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -31861,6 +31861,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1212" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="G1212" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="H1212" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -31939,6 +31939,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1215" t="n">
+        <v>9250</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>14</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G1215" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H1215" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28379,8 +28379,31 @@
       <c r="E1218" t="n">
         <v>14.8999996185303</v>
       </c>
-      <c r="F1218"/>
+      <c r="F1218" t="n">
+        <v>15.0500001907349</v>
+      </c>
       <c r="G1218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>15.1000003814697</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="F1219"/>
+      <c r="G1219" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28402,8 +28402,31 @@
       <c r="E1219" t="n">
         <v>14.5500001907349</v>
       </c>
-      <c r="F1219"/>
+      <c r="F1219" t="n">
+        <v>14.6999998092651</v>
+      </c>
       <c r="G1219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="F1220"/>
+      <c r="G1220" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28425,8 +28425,31 @@
       <c r="E1220" t="n">
         <v>14.8999996185303</v>
       </c>
-      <c r="F1220"/>
+      <c r="F1220" t="n">
+        <v>14.75</v>
+      </c>
       <c r="G1220" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1221"/>
+      <c r="G1221" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28448,8 +28448,31 @@
       <c r="E1221" t="n">
         <v>15</v>
       </c>
-      <c r="F1221"/>
+      <c r="F1221" t="n">
+        <v>14.75</v>
+      </c>
       <c r="G1221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1222" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="F1222"/>
+      <c r="G1222" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28478,6 +28478,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1223">
+      <c r="A1223" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1223" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>14.6499996185303</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="G1223" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -28501,6 +28501,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1224" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -32251,6 +32251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1227" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="H1227" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -35961,6 +35961,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1228" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>500</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1229" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>14.5500001907349</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -36019,6 +36019,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1230" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="H1230" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1230" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -36048,6 +36048,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1231">
+      <c r="A1231" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1231" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1232" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="H1232" t="n">
+        <v>250</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -36106,6 +36106,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1233">
+      <c r="A1233" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1233" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>14.0500001907349</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H1233" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1233" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -36135,6 +36135,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1234" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="H1234" t="n">
+        <v>750</v>
+      </c>
+      <c r="I1234" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -36164,6 +36164,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1235">
+      <c r="A1235" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1235" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>13.6000003814697</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="H1235" t="n">
+        <v>6750</v>
+      </c>
+      <c r="I1235" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -36193,6 +36193,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1236">
+      <c r="A1236" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1236" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1236" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>14.1499996185303</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="H1236" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1236" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDB.MI.xlsx
+++ b/data/LDB.MI.xlsx
@@ -36222,6 +36222,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1237">
+      <c r="A1237" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1237" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>14.4499998092651</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="H1237" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I1237" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
